--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I635"/>
+  <dimension ref="A1:I637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21371,6 +21371,72 @@
         <v>385.58</v>
       </c>
       <c r="I635" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>360.26</v>
+      </c>
+      <c r="C636" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="D636" t="n">
+        <v>367.23</v>
+      </c>
+      <c r="E636" t="n">
+        <v>373.86</v>
+      </c>
+      <c r="F636" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="G636" t="n">
+        <v>375.92</v>
+      </c>
+      <c r="H636" t="n">
+        <v>381.46</v>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="n">
+        <v>361.44</v>
+      </c>
+      <c r="C637" t="n">
+        <v>366.86</v>
+      </c>
+      <c r="D637" t="n">
+        <v>367.48</v>
+      </c>
+      <c r="E637" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="F637" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="G637" t="n">
+        <v>376.13</v>
+      </c>
+      <c r="H637" t="n">
+        <v>381.28</v>
+      </c>
+      <c r="I637" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21387,7 +21453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B661"/>
+  <dimension ref="A1:B663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28000,6 +28066,26 @@
       </c>
       <c r="B661" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B662" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B663" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>
@@ -28168,28 +28254,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05838780626355906</v>
+        <v>0.05375495382726386</v>
       </c>
       <c r="J2" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K2" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L2" t="n">
-        <v>0.005668274263670559</v>
+        <v>0.004819046965126472</v>
       </c>
       <c r="M2" t="n">
-        <v>4.61020857412003</v>
+        <v>4.619059467625122</v>
       </c>
       <c r="N2" t="n">
-        <v>32.24598340962078</v>
+        <v>32.30626522126499</v>
       </c>
       <c r="O2" t="n">
-        <v>5.67855469372452</v>
+        <v>5.683860063483705</v>
       </c>
       <c r="P2" t="n">
-        <v>366.4930253835308</v>
+        <v>366.5413002277288</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28250,28 +28336,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03251455598637085</v>
+        <v>-0.03796039857317701</v>
       </c>
       <c r="J3" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K3" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00574718948435271</v>
+        <v>0.007700426525494963</v>
       </c>
       <c r="M3" t="n">
-        <v>2.491368379900404</v>
+        <v>2.511225885033185</v>
       </c>
       <c r="N3" t="n">
-        <v>9.8616102768822</v>
+        <v>10.05306341484895</v>
       </c>
       <c r="O3" t="n">
-        <v>3.140320091468734</v>
+        <v>3.17065662203414</v>
       </c>
       <c r="P3" t="n">
-        <v>375.8069064234287</v>
+        <v>375.8636528484297</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28332,28 +28418,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.004258798255542777</v>
+        <v>0.002205427970514617</v>
       </c>
       <c r="J4" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K4" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L4" t="n">
-        <v>7.463518619466036e-05</v>
+        <v>2.011158823278514e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.756312671746324</v>
+        <v>2.757830490772939</v>
       </c>
       <c r="N4" t="n">
-        <v>13.17087257543812</v>
+        <v>13.16132419136538</v>
       </c>
       <c r="O4" t="n">
-        <v>3.629169681268447</v>
+        <v>3.627853937435379</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4410117165978</v>
+        <v>370.4623282276269</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28414,28 +28500,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04578503205239934</v>
+        <v>-0.04773959736659227</v>
       </c>
       <c r="J5" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K5" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009696601248816883</v>
+        <v>0.01058223441073125</v>
       </c>
       <c r="M5" t="n">
-        <v>2.513194176981973</v>
+        <v>2.514392580141379</v>
       </c>
       <c r="N5" t="n">
-        <v>11.60412041113962</v>
+        <v>11.59654890289885</v>
       </c>
       <c r="O5" t="n">
-        <v>3.406482116662235</v>
+        <v>3.405370596998049</v>
       </c>
       <c r="P5" t="n">
-        <v>378.2781620726809</v>
+        <v>378.2984528476859</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28496,28 +28582,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07222432087381889</v>
+        <v>-0.07386674634807036</v>
       </c>
       <c r="J6" t="n">
+        <v>636</v>
+      </c>
+      <c r="K6" t="n">
         <v>634</v>
       </c>
-      <c r="K6" t="n">
-        <v>632</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.02978381488177995</v>
+        <v>0.03126041947178904</v>
       </c>
       <c r="M6" t="n">
-        <v>2.298990489013908</v>
+        <v>2.299113670829058</v>
       </c>
       <c r="N6" t="n">
-        <v>9.174997912854916</v>
+        <v>9.166745297559435</v>
       </c>
       <c r="O6" t="n">
-        <v>3.029025901648072</v>
+        <v>3.027663339534208</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2234865439032</v>
+        <v>379.2405935494157</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28578,28 +28664,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01341059456122537</v>
+        <v>-0.01484789846230233</v>
       </c>
       <c r="J7" t="n">
+        <v>636</v>
+      </c>
+      <c r="K7" t="n">
         <v>634</v>
       </c>
-      <c r="K7" t="n">
-        <v>632</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.000769578410199756</v>
+        <v>0.0009488522046356973</v>
       </c>
       <c r="M7" t="n">
-        <v>2.851850247513289</v>
+        <v>2.849125442850253</v>
       </c>
       <c r="N7" t="n">
-        <v>12.60839153955131</v>
+        <v>12.58415653188566</v>
       </c>
       <c r="O7" t="n">
-        <v>3.550829697345582</v>
+        <v>3.547415472126949</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6075435117929</v>
+        <v>378.6225141195105</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28660,28 +28746,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02200530823702083</v>
+        <v>0.01936058901934845</v>
       </c>
       <c r="J8" t="n">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="K8" t="n">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002116803254324728</v>
+        <v>0.001644109630131285</v>
       </c>
       <c r="M8" t="n">
-        <v>2.775195394420019</v>
+        <v>2.778529136957333</v>
       </c>
       <c r="N8" t="n">
-        <v>12.37048870101827</v>
+        <v>12.38404492181447</v>
       </c>
       <c r="O8" t="n">
-        <v>3.517170553302507</v>
+        <v>3.519097174250019</v>
       </c>
       <c r="P8" t="n">
-        <v>384.8909409281205</v>
+        <v>384.9184825345206</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -28723,7 +28809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I635"/>
+  <dimension ref="A1:I637"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58523,6 +58609,100 @@
         </is>
       </c>
     </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>-36.556186190728376,174.70740881508016</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>-36.55688669305564,174.70726920069316</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>-36.55759636078655,174.70733533434557</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>-36.55829731360697,174.70752299146116</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>-36.55899759377444,174.7076997557536</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>-36.55969350933059,174.70792542790923</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>-36.56038088756875,174.7081885429266</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>-36.55618850335837,174.70742168158822</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>-36.556887148665126,174.7072770001524</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>-36.557596120077584,174.70733811120118</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>-36.558296802335335,174.70752662316082</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>-36.55899605914021,174.7077080302906</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>-36.559693052756394,174.70792770466858</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>-36.560381273626156,174.7081865897825</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I637"/>
+  <dimension ref="A1:I639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21437,6 +21437,72 @@
         <v>381.28</v>
       </c>
       <c r="I637" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="n">
+        <v>360.98</v>
+      </c>
+      <c r="C638" t="n">
+        <v>367.78</v>
+      </c>
+      <c r="D638" t="n">
+        <v>366.3</v>
+      </c>
+      <c r="E638" t="n">
+        <v>374.05</v>
+      </c>
+      <c r="F638" t="n">
+        <v>375.32</v>
+      </c>
+      <c r="G638" t="n">
+        <v>376.01</v>
+      </c>
+      <c r="H638" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="n">
+        <v>361.76</v>
+      </c>
+      <c r="C639" t="n">
+        <v>369.09</v>
+      </c>
+      <c r="D639" t="n">
+        <v>367.1</v>
+      </c>
+      <c r="E639" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="F639" t="n">
+        <v>376.39</v>
+      </c>
+      <c r="G639" t="n">
+        <v>377.19</v>
+      </c>
+      <c r="H639" t="n">
+        <v>382.5</v>
+      </c>
+      <c r="I639" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21453,7 +21519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B663"/>
+  <dimension ref="A1:B665"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28086,6 +28152,26 @@
       </c>
       <c r="B663" t="n">
         <v>1.39</v>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B664" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B665" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -28254,28 +28340,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.05375495382726386</v>
+        <v>0.0495182885566321</v>
       </c>
       <c r="J2" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K2" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004819046965126472</v>
+        <v>0.004104543453482656</v>
       </c>
       <c r="M2" t="n">
-        <v>4.619059467625122</v>
+        <v>4.626289765556902</v>
       </c>
       <c r="N2" t="n">
-        <v>32.30626522126499</v>
+        <v>32.34050917916054</v>
       </c>
       <c r="O2" t="n">
-        <v>5.683860063483705</v>
+        <v>5.686871651370422</v>
       </c>
       <c r="P2" t="n">
-        <v>366.5413002277288</v>
+        <v>366.5855689300512</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -28336,28 +28422,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.03796039857317701</v>
+        <v>-0.04208648494005966</v>
       </c>
       <c r="J3" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K3" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L3" t="n">
-        <v>0.007700426525494963</v>
+        <v>0.009395899366126059</v>
       </c>
       <c r="M3" t="n">
-        <v>2.511225885033185</v>
+        <v>2.524576103959394</v>
       </c>
       <c r="N3" t="n">
-        <v>10.05306341484895</v>
+        <v>10.15111580565685</v>
       </c>
       <c r="O3" t="n">
-        <v>3.17065662203414</v>
+        <v>3.186081575486862</v>
       </c>
       <c r="P3" t="n">
-        <v>375.8636528484297</v>
+        <v>375.9067643894706</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -28418,28 +28504,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002205427970514617</v>
+        <v>-0.0002389777494749381</v>
       </c>
       <c r="J4" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K4" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L4" t="n">
-        <v>2.011158823278514e-05</v>
+        <v>2.370197988987854e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.757830490772939</v>
+        <v>2.761301727475842</v>
       </c>
       <c r="N4" t="n">
-        <v>13.16132419136538</v>
+        <v>13.16592753610251</v>
       </c>
       <c r="O4" t="n">
-        <v>3.627853937435379</v>
+        <v>3.62848832657658</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4623282276269</v>
+        <v>370.4877735808319</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -28500,28 +28586,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04773959736659227</v>
+        <v>-0.04929893252716489</v>
       </c>
       <c r="J5" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K5" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01058223441073125</v>
+        <v>0.01133834887440366</v>
       </c>
       <c r="M5" t="n">
-        <v>2.514392580141379</v>
+        <v>2.513742087209383</v>
       </c>
       <c r="N5" t="n">
-        <v>11.59654890289885</v>
+        <v>11.57961601576602</v>
       </c>
       <c r="O5" t="n">
-        <v>3.405370596998049</v>
+        <v>3.402883485481984</v>
       </c>
       <c r="P5" t="n">
-        <v>378.2984528476859</v>
+        <v>378.3146831207087</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -28582,28 +28668,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07386674634807036</v>
+        <v>-0.07478393704426194</v>
       </c>
       <c r="J6" t="n">
+        <v>638</v>
+      </c>
+      <c r="K6" t="n">
         <v>636</v>
       </c>
-      <c r="K6" t="n">
-        <v>634</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03126041947178904</v>
+        <v>0.03221532382926451</v>
       </c>
       <c r="M6" t="n">
-        <v>2.299113670829058</v>
+        <v>2.295984613607214</v>
       </c>
       <c r="N6" t="n">
-        <v>9.166745297559435</v>
+        <v>9.145171407168366</v>
       </c>
       <c r="O6" t="n">
-        <v>3.027663339534208</v>
+        <v>3.024098445350013</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2405935494157</v>
+        <v>379.2501704849645</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -28664,28 +28750,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01484789846230233</v>
+        <v>-0.0158943378998707</v>
       </c>
       <c r="J7" t="n">
+        <v>638</v>
+      </c>
+      <c r="K7" t="n">
         <v>636</v>
       </c>
-      <c r="K7" t="n">
-        <v>634</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.0009488522046356973</v>
+        <v>0.001094177707379851</v>
       </c>
       <c r="M7" t="n">
-        <v>2.849125442850253</v>
+        <v>2.844689963152982</v>
       </c>
       <c r="N7" t="n">
-        <v>12.58415653188566</v>
+        <v>12.55395376477254</v>
       </c>
       <c r="O7" t="n">
-        <v>3.547415472126949</v>
+        <v>3.543155904666424</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6225141195105</v>
+        <v>378.633440733191</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -28746,28 +28832,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01936058901934845</v>
+        <v>0.01709329488465836</v>
       </c>
       <c r="J8" t="n">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="K8" t="n">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001644109630131285</v>
+        <v>0.001287075859423337</v>
       </c>
       <c r="M8" t="n">
-        <v>2.778529136957333</v>
+        <v>2.78006471642527</v>
       </c>
       <c r="N8" t="n">
-        <v>12.38404492181447</v>
+        <v>12.38502394693129</v>
       </c>
       <c r="O8" t="n">
-        <v>3.519097174250019</v>
+        <v>3.519236273246126</v>
       </c>
       <c r="P8" t="n">
-        <v>384.9184825345206</v>
+        <v>384.9421572255546</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -28809,7 +28895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I637"/>
+  <dimension ref="A1:I639"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58703,6 +58789,100 @@
         </is>
       </c>
     </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>-36.55618760182482,174.70741666583075</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>-36.55688774746538,174.7072872508704</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>-36.557597256223325,174.70732500444262</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>-36.55829701923846,174.70752508243976</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>-36.55899571586669,174.70770988117383</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>-36.55969331365594,174.70792640366324</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>-36.56038123073088,174.70818680679852</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>-36.55618913051203,174.70742517081084</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>-36.55688860010334,174.7073018470016</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>-36.55759648595519,174.70733389038068</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>-36.558295314999,174.707537188105</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>-36.5589935552621,174.7077215308502</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>-36.5596907481431,174.707939196882</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>-36.56037865701428,174.7081998277585</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I639"/>
+  <dimension ref="A1:I640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21503,6 +21503,39 @@
         <v>382.5</v>
       </c>
       <c r="I639" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="n">
+        <v>362.81</v>
+      </c>
+      <c r="C640" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="D640" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="E640" t="n">
+        <v>374.45</v>
+      </c>
+      <c r="F640" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="G640" t="n">
+        <v>376.56</v>
+      </c>
+      <c r="H640" t="n">
+        <v>381.42</v>
+      </c>
+      <c r="I640" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21519,7 +21552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B665"/>
+  <dimension ref="A1:B666"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28172,6 +28205,16 @@
       </c>
       <c r="B665" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B666" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -28340,34 +28383,30 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0495182885566321</v>
+        <v>0.04787620710101621</v>
       </c>
       <c r="J2" t="n">
+        <v>639</v>
+      </c>
+      <c r="K2" t="n">
         <v>638</v>
       </c>
-      <c r="K2" t="n">
-        <v>637</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.004104543453482656</v>
+        <v>0.003846973468381476</v>
       </c>
       <c r="M2" t="n">
-        <v>4.626289765556902</v>
+        <v>4.627463627019567</v>
       </c>
       <c r="N2" t="n">
-        <v>32.34050917916054</v>
+        <v>32.33020338089803</v>
       </c>
       <c r="O2" t="n">
-        <v>5.686871651370422</v>
+        <v>5.685965474824661</v>
       </c>
       <c r="P2" t="n">
-        <v>366.5855689300512</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>366.6028061499826</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.70348063815126 -36.55548006709824, 174.7135291326469 -36.55728608474668)</t>
@@ -28422,34 +28461,30 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04208648494005966</v>
+        <v>-0.04360996578523805</v>
       </c>
       <c r="J3" t="n">
+        <v>639</v>
+      </c>
+      <c r="K3" t="n">
         <v>638</v>
       </c>
-      <c r="K3" t="n">
-        <v>637</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.009395899366126059</v>
+        <v>0.0100835302956136</v>
       </c>
       <c r="M3" t="n">
-        <v>2.524576103959394</v>
+        <v>2.528500670030593</v>
       </c>
       <c r="N3" t="n">
-        <v>10.15111580565685</v>
+        <v>10.16996666368766</v>
       </c>
       <c r="O3" t="n">
-        <v>3.186081575486862</v>
+        <v>3.189038517121996</v>
       </c>
       <c r="P3" t="n">
-        <v>375.9067643894706</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>375.9227566377842</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.703189424756 -36.5566482999418, 174.71345810486915 -36.55724805854378)</t>
@@ -28504,34 +28539,30 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0002389777494749381</v>
+        <v>-0.00196769098554048</v>
       </c>
       <c r="J4" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K4" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L4" t="n">
-        <v>2.370197988987854e-07</v>
+        <v>1.607169905215589e-05</v>
       </c>
       <c r="M4" t="n">
-        <v>2.761301727475842</v>
+        <v>2.765545766149226</v>
       </c>
       <c r="N4" t="n">
-        <v>13.16592753610251</v>
+        <v>13.1904262353223</v>
       </c>
       <c r="O4" t="n">
-        <v>3.62848832657658</v>
+        <v>3.631862639930411</v>
       </c>
       <c r="P4" t="n">
-        <v>370.4877735808319</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>370.5058530477193</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.70325633425622 -36.557949873611484, 174.7134929320932 -36.55706243340639)</t>
@@ -28586,34 +28617,30 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04929893252716489</v>
+        <v>-0.05012015236813106</v>
       </c>
       <c r="J5" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K5" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01133834887440366</v>
+        <v>0.01174656162346888</v>
       </c>
       <c r="M5" t="n">
-        <v>2.513742087209383</v>
+        <v>2.513585426225163</v>
       </c>
       <c r="N5" t="n">
-        <v>11.57961601576602</v>
+        <v>11.57167284649615</v>
       </c>
       <c r="O5" t="n">
-        <v>3.402883485481984</v>
+        <v>3.401716161953573</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3146831207087</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>378.3232717151686</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.7034085723803 -36.55887646759057, 174.7135506053018 -36.557448583717985)</t>
@@ -28668,34 +28695,30 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07478393704426194</v>
+        <v>-0.0753237569083456</v>
       </c>
       <c r="J6" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K6" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03221532382926451</v>
+        <v>0.03276651282741538</v>
       </c>
       <c r="M6" t="n">
-        <v>2.295984613607214</v>
+        <v>2.294779423888308</v>
       </c>
       <c r="N6" t="n">
-        <v>9.145171407168366</v>
+        <v>9.135187500343932</v>
       </c>
       <c r="O6" t="n">
-        <v>3.024098445350013</v>
+        <v>3.022447270068402</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2501704849645</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.2558347956455</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.7036235239375 -36.55975351400116, 174.71365683149145 -36.557892603378356)</t>
@@ -28750,34 +28773,30 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0158943378998707</v>
+        <v>-0.01642830413268821</v>
       </c>
       <c r="J7" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K7" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001094177707379851</v>
+        <v>0.001172686361470054</v>
       </c>
       <c r="M7" t="n">
-        <v>2.844689963152982</v>
+        <v>2.842501212419613</v>
       </c>
       <c r="N7" t="n">
-        <v>12.55395376477254</v>
+        <v>12.53852423271704</v>
       </c>
       <c r="O7" t="n">
-        <v>3.543155904666424</v>
+        <v>3.540977863912317</v>
       </c>
       <c r="P7" t="n">
-        <v>378.633440733191</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>378.6390436219266</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.70384976624126 -36.560510751969275, 174.71384068050895 -36.55850711930926)</t>
@@ -28832,34 +28851,30 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01709329488465836</v>
+        <v>0.01581153065122462</v>
       </c>
       <c r="J8" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="K8" t="n">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001287075859423337</v>
+        <v>0.001103271434518827</v>
       </c>
       <c r="M8" t="n">
-        <v>2.78006471642527</v>
+        <v>2.781451483919516</v>
       </c>
       <c r="N8" t="n">
-        <v>12.38502394693129</v>
+        <v>12.3902565519987</v>
       </c>
       <c r="O8" t="n">
-        <v>3.519236273246126</v>
+        <v>3.519979623804476</v>
       </c>
       <c r="P8" t="n">
-        <v>384.9421572255546</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>384.955605043838</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.70404935027682 -36.561198958216586, 174.71404863607273 -36.55922242438897)</t>
@@ -28895,7 +28910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I639"/>
+  <dimension ref="A1:I640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58883,6 +58898,53 @@
         </is>
       </c>
     </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>-36.55619118835923,174.70743661982303</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>-36.55688923795346,174.70731276624497</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>-36.5575984116243,174.70731167553515</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>-36.55829639951517,174.7075294844999</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>-36.55899517066751,174.70771282081185</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>-36.55969211786622,174.7079323666043</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>-36.56038097335928,174.70818810889457</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I640"/>
+  <dimension ref="A1:I642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21536,6 +21536,72 @@
         <v>381.42</v>
       </c>
       <c r="I640" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="C641" t="n">
+        <v>369.17</v>
+      </c>
+      <c r="D641" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="E641" t="n">
+        <v>373.9</v>
+      </c>
+      <c r="F641" t="n">
+        <v>375.47</v>
+      </c>
+      <c r="G641" t="n">
+        <v>375.78</v>
+      </c>
+      <c r="H641" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="C642" t="n">
+        <v>370.74</v>
+      </c>
+      <c r="D642" t="n">
+        <v>366.54</v>
+      </c>
+      <c r="E642" t="n">
+        <v>375.22</v>
+      </c>
+      <c r="F642" t="n">
+        <v>376.23</v>
+      </c>
+      <c r="G642" t="n">
+        <v>376.8</v>
+      </c>
+      <c r="H642" t="n">
+        <v>383.23</v>
+      </c>
+      <c r="I642" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21552,7 +21618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B666"/>
+  <dimension ref="A1:B668"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28215,6 +28281,26 @@
       </c>
       <c r="B666" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B667" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B668" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -28383,28 +28469,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04787620710101621</v>
+        <v>0.04573299226943797</v>
       </c>
       <c r="J2" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K2" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003846973468381476</v>
+        <v>0.003532540477948154</v>
       </c>
       <c r="M2" t="n">
-        <v>4.627463627019567</v>
+        <v>4.623938386063372</v>
       </c>
       <c r="N2" t="n">
-        <v>32.33020338089803</v>
+        <v>32.26837208352201</v>
       </c>
       <c r="O2" t="n">
-        <v>5.685965474824661</v>
+        <v>5.680525687251314</v>
       </c>
       <c r="P2" t="n">
-        <v>366.6028061499826</v>
+        <v>366.6253288670659</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28461,28 +28547,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04360996578523805</v>
+        <v>-0.04668832461823735</v>
       </c>
       <c r="J3" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K3" t="n">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0100835302956136</v>
+        <v>0.01154047566155136</v>
       </c>
       <c r="M3" t="n">
-        <v>2.528500670030593</v>
+        <v>2.536735745928145</v>
       </c>
       <c r="N3" t="n">
-        <v>10.16996666368766</v>
+        <v>10.21159558898735</v>
       </c>
       <c r="O3" t="n">
-        <v>3.189038517121996</v>
+        <v>3.195558728765183</v>
       </c>
       <c r="P3" t="n">
-        <v>375.9227566377842</v>
+        <v>375.9551098837074</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28539,28 +28625,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.00196769098554048</v>
+        <v>-0.004999355043013248</v>
       </c>
       <c r="J4" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K4" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L4" t="n">
-        <v>1.607169905215589e-05</v>
+        <v>0.0001039190515298438</v>
       </c>
       <c r="M4" t="n">
-        <v>2.765545766149226</v>
+        <v>2.772077606808527</v>
       </c>
       <c r="N4" t="n">
-        <v>13.1904262353223</v>
+        <v>13.22134385208399</v>
       </c>
       <c r="O4" t="n">
-        <v>3.631862639930411</v>
+        <v>3.636116589451442</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5058530477193</v>
+        <v>370.5375976035472</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28617,28 +28703,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05012015236813106</v>
+        <v>-0.05166750545582207</v>
       </c>
       <c r="J5" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K5" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01174656162346888</v>
+        <v>0.01254200260694815</v>
       </c>
       <c r="M5" t="n">
-        <v>2.513585426225163</v>
+        <v>2.512818744596859</v>
       </c>
       <c r="N5" t="n">
-        <v>11.57167284649615</v>
+        <v>11.5551258581417</v>
       </c>
       <c r="O5" t="n">
-        <v>3.401716161953573</v>
+        <v>3.39928313886056</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3232717151686</v>
+        <v>378.3394732660782</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28695,28 +28781,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0753237569083456</v>
+        <v>-0.07621983504940928</v>
       </c>
       <c r="J6" t="n">
+        <v>641</v>
+      </c>
+      <c r="K6" t="n">
         <v>639</v>
       </c>
-      <c r="K6" t="n">
-        <v>637</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03276651282741538</v>
+        <v>0.03373597639335768</v>
       </c>
       <c r="M6" t="n">
-        <v>2.294779423888308</v>
+        <v>2.291579336734527</v>
       </c>
       <c r="N6" t="n">
-        <v>9.135187500343932</v>
+        <v>9.113115218354421</v>
       </c>
       <c r="O6" t="n">
-        <v>3.022447270068402</v>
+        <v>3.018793669390875</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2558347956455</v>
+        <v>379.2652482199371</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28773,28 +28859,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01642830413268821</v>
+        <v>-0.0176520584873773</v>
       </c>
       <c r="J7" t="n">
+        <v>641</v>
+      </c>
+      <c r="K7" t="n">
         <v>639</v>
       </c>
-      <c r="K7" t="n">
-        <v>637</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001172686361470054</v>
+        <v>0.001362137083284365</v>
       </c>
       <c r="M7" t="n">
-        <v>2.842501212419613</v>
+        <v>2.838791520082429</v>
       </c>
       <c r="N7" t="n">
-        <v>12.53852423271704</v>
+        <v>12.51140991626087</v>
       </c>
       <c r="O7" t="n">
-        <v>3.540977863912317</v>
+        <v>3.537147143710715</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6390436219266</v>
+        <v>378.651899362109</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28851,28 +28937,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01581153065122462</v>
+        <v>0.01388144767380063</v>
       </c>
       <c r="J8" t="n">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="K8" t="n">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001103271434518827</v>
+        <v>0.0008546019177390063</v>
       </c>
       <c r="M8" t="n">
-        <v>2.781451483919516</v>
+        <v>2.781357810246206</v>
       </c>
       <c r="N8" t="n">
-        <v>12.3902565519987</v>
+        <v>12.38193872318243</v>
       </c>
       <c r="O8" t="n">
-        <v>3.519979623804476</v>
+        <v>3.518797908829438</v>
       </c>
       <c r="P8" t="n">
-        <v>384.955605043838</v>
+        <v>384.9758783092925</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28910,7 +28996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I640"/>
+  <dimension ref="A1:I642"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58945,6 +59031,100 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>-36.55619218788461,174.707442180772</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>-36.55688865217277,174.7073027383684</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>-36.55759865233265,174.70730889867937</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>-36.558297251634656,174.70752343166717</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>-36.55899541297827,174.70771151430608</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>-36.55969381371336,174.70792391006964</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>-36.56038082322585,174.70818886845058</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>-36.556196911128424,174.70746845898364</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>-36.55688967403409,174.70732023144205</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>-36.55759702514296,174.70732767022406</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>-36.55829520654737,174.7075379584655</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>-36.55899387834322,174.70771978884255</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>-36.559691596066976,174.70793496861486</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>-36.560377091335994,174.70820774884206</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I642"/>
+  <dimension ref="A1:I644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21602,6 +21602,72 @@
         <v>383.23</v>
       </c>
       <c r="I642" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="n">
+        <v>365.39</v>
+      </c>
+      <c r="C643" t="n">
+        <v>370.05</v>
+      </c>
+      <c r="D643" t="n">
+        <v>365.8</v>
+      </c>
+      <c r="E643" t="n">
+        <v>374.18</v>
+      </c>
+      <c r="F643" t="n">
+        <v>375.66</v>
+      </c>
+      <c r="G643" t="n">
+        <v>376.26</v>
+      </c>
+      <c r="H643" t="n">
+        <v>382.25</v>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="n">
+        <v>365.65</v>
+      </c>
+      <c r="C644" t="n">
+        <v>370.73</v>
+      </c>
+      <c r="D644" t="n">
+        <v>365.57</v>
+      </c>
+      <c r="E644" t="n">
+        <v>375.14</v>
+      </c>
+      <c r="F644" t="n">
+        <v>376.15</v>
+      </c>
+      <c r="G644" t="n">
+        <v>376.91</v>
+      </c>
+      <c r="H644" t="n">
+        <v>382.26</v>
+      </c>
+      <c r="I644" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -21618,7 +21684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B668"/>
+  <dimension ref="A1:B670"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28301,6 +28367,26 @@
       </c>
       <c r="B668" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B669" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B670" t="n">
+        <v>1.18</v>
       </c>
     </row>
   </sheetData>
@@ -28469,28 +28555,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04573299226943797</v>
+        <v>0.04425221635744581</v>
       </c>
       <c r="J2" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K2" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003532540477948154</v>
+        <v>0.003330384335343273</v>
       </c>
       <c r="M2" t="n">
-        <v>4.623938386063372</v>
+        <v>4.617018745218176</v>
       </c>
       <c r="N2" t="n">
-        <v>32.26837208352201</v>
+        <v>32.1845296014695</v>
       </c>
       <c r="O2" t="n">
-        <v>5.680525687251314</v>
+        <v>5.673141070118872</v>
       </c>
       <c r="P2" t="n">
-        <v>366.6253288670659</v>
+        <v>366.6409347423071</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28547,28 +28633,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04668832461823735</v>
+        <v>-0.04944033791635823</v>
       </c>
       <c r="J3" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K3" t="n">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01154047566155136</v>
+        <v>0.01294278072386046</v>
       </c>
       <c r="M3" t="n">
-        <v>2.536735745928145</v>
+        <v>2.543487939836529</v>
       </c>
       <c r="N3" t="n">
-        <v>10.21159558898735</v>
+        <v>10.2375926481324</v>
       </c>
       <c r="O3" t="n">
-        <v>3.195558728765183</v>
+        <v>3.19962382916061</v>
       </c>
       <c r="P3" t="n">
-        <v>375.9551098837074</v>
+        <v>375.9841130349004</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28625,28 +28711,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.004999355043013248</v>
+        <v>-0.007995529205914943</v>
       </c>
       <c r="J4" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K4" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0001039190515298438</v>
+        <v>0.0002662936471771182</v>
       </c>
       <c r="M4" t="n">
-        <v>2.772077606808527</v>
+        <v>2.778593175617947</v>
       </c>
       <c r="N4" t="n">
-        <v>13.22134385208399</v>
+        <v>13.24886583117812</v>
       </c>
       <c r="O4" t="n">
-        <v>3.636116589451442</v>
+        <v>3.639899151237314</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5375976035472</v>
+        <v>370.5690589771588</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28703,28 +28789,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05166750545582207</v>
+        <v>-0.05312927344662172</v>
       </c>
       <c r="J5" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K5" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01254200260694815</v>
+        <v>0.01332714877216201</v>
       </c>
       <c r="M5" t="n">
-        <v>2.512818744596859</v>
+        <v>2.511644060276128</v>
       </c>
       <c r="N5" t="n">
-        <v>11.5551258581417</v>
+        <v>11.53624396236514</v>
       </c>
       <c r="O5" t="n">
-        <v>3.39928313886056</v>
+        <v>3.396504668385595</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3394732660782</v>
+        <v>378.3548211561448</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28781,28 +28867,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07621983504940928</v>
+        <v>-0.07706794697409271</v>
       </c>
       <c r="J6" t="n">
+        <v>643</v>
+      </c>
+      <c r="K6" t="n">
         <v>641</v>
       </c>
-      <c r="K6" t="n">
-        <v>639</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.03373597639335768</v>
+        <v>0.03468482475678947</v>
       </c>
       <c r="M6" t="n">
-        <v>2.291579336734527</v>
+        <v>2.288185952190549</v>
       </c>
       <c r="N6" t="n">
-        <v>9.113115218354421</v>
+        <v>9.090339519078046</v>
       </c>
       <c r="O6" t="n">
-        <v>3.018793669390875</v>
+        <v>3.015018991495418</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2652482199371</v>
+        <v>379.2741824967295</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28859,28 +28945,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0176520584873773</v>
+        <v>-0.01866848959206302</v>
       </c>
       <c r="J7" t="n">
+        <v>643</v>
+      </c>
+      <c r="K7" t="n">
         <v>641</v>
       </c>
-      <c r="K7" t="n">
-        <v>639</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.001362137083284365</v>
+        <v>0.001533277958459256</v>
       </c>
       <c r="M7" t="n">
-        <v>2.838791520082429</v>
+        <v>2.834203331798542</v>
       </c>
       <c r="N7" t="n">
-        <v>12.51140991626087</v>
+        <v>12.48055681517607</v>
       </c>
       <c r="O7" t="n">
-        <v>3.537147143710715</v>
+        <v>3.532783154281631</v>
       </c>
       <c r="P7" t="n">
-        <v>378.651899362109</v>
+        <v>378.6626066882617</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28937,28 +29023,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01388144767380063</v>
+        <v>0.01190953702443593</v>
       </c>
       <c r="J8" t="n">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="K8" t="n">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008546019177390063</v>
+        <v>0.0006322092679450497</v>
       </c>
       <c r="M8" t="n">
-        <v>2.781357810246206</v>
+        <v>2.781582256650367</v>
       </c>
       <c r="N8" t="n">
-        <v>12.38193872318243</v>
+        <v>12.3727815840151</v>
       </c>
       <c r="O8" t="n">
-        <v>3.518797908829438</v>
+        <v>3.517496493817029</v>
       </c>
       <c r="P8" t="n">
-        <v>384.9758783092925</v>
+        <v>384.9966506758573</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28996,7 +29082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I642"/>
+  <dimension ref="A1:I644"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59125,6 +59211,100 @@
         </is>
       </c>
     </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>-36.55619624477904,174.7074647516839</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>-36.55688922493613,174.70731254340328</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>-36.55759773764058,174.70731945073123</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>-36.55829681782841,174.70752651310931</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>-36.55899502931956,174.70771358294022</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>-36.55969277011519,174.70792911409103</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>-36.56037919320536,174.7081971150586</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>-36.55619675434035,174.7074675866778</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>-36.55688966752543,174.7073201200212</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>-36.55759795909242,174.70731689602397</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>-36.55829533049209,174.7075370780535</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>-36.55899403988378,174.70771891783872</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>-36.55969135690897,174.70793616120307</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>-36.560379171757724,174.7081972235666</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I644"/>
+  <dimension ref="A1:I651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21670,6 +21670,237 @@
       <c r="I644" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="n">
+        <v>365.68</v>
+      </c>
+      <c r="C645" t="n">
+        <v>372.48</v>
+      </c>
+      <c r="D645" t="n">
+        <v>365.9</v>
+      </c>
+      <c r="E645" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="F645" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="G645" t="n">
+        <v>377.49</v>
+      </c>
+      <c r="H645" t="n">
+        <v>383.07</v>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="n">
+        <v>365.2</v>
+      </c>
+      <c r="C646" t="n">
+        <v>372.62</v>
+      </c>
+      <c r="D646" t="n">
+        <v>366.1</v>
+      </c>
+      <c r="E646" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="F646" t="n">
+        <v>375.84</v>
+      </c>
+      <c r="G646" t="n">
+        <v>377.33</v>
+      </c>
+      <c r="H646" t="n">
+        <v>383.13</v>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="n">
+        <v>365.16</v>
+      </c>
+      <c r="C647" t="n">
+        <v>372.25</v>
+      </c>
+      <c r="D647" t="n">
+        <v>366.07</v>
+      </c>
+      <c r="E647" t="n">
+        <v>375.12</v>
+      </c>
+      <c r="F647" t="n">
+        <v>375.23</v>
+      </c>
+      <c r="G647" t="n">
+        <v>376.38</v>
+      </c>
+      <c r="H647" t="n">
+        <v>382.31</v>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="n">
+        <v>365.07</v>
+      </c>
+      <c r="C648" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="D648" t="n">
+        <v>366.98</v>
+      </c>
+      <c r="E648" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="F648" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="G648" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="H648" t="n">
+        <v>383.34</v>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="C649" t="n">
+        <v>373.42</v>
+      </c>
+      <c r="D649" t="n">
+        <v>367.34</v>
+      </c>
+      <c r="E649" t="n">
+        <v>376.24</v>
+      </c>
+      <c r="F649" t="n">
+        <v>375.59</v>
+      </c>
+      <c r="G649" t="n">
+        <v>376.97</v>
+      </c>
+      <c r="H649" t="n">
+        <v>383.23</v>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="n">
+        <v>364.01</v>
+      </c>
+      <c r="C650" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="D650" t="n">
+        <v>367.81</v>
+      </c>
+      <c r="E650" t="n">
+        <v>376.14</v>
+      </c>
+      <c r="F650" t="n">
+        <v>375.43</v>
+      </c>
+      <c r="G650" t="n">
+        <v>376.71</v>
+      </c>
+      <c r="H650" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="n">
+        <v>363.25</v>
+      </c>
+      <c r="C651" t="n">
+        <v>373.2</v>
+      </c>
+      <c r="D651" t="n">
+        <v>368.23</v>
+      </c>
+      <c r="E651" t="n">
+        <v>376.68</v>
+      </c>
+      <c r="F651" t="n">
+        <v>375.68</v>
+      </c>
+      <c r="G651" t="n">
+        <v>377.16</v>
+      </c>
+      <c r="H651" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28387,6 +28618,76 @@
       </c>
       <c r="B670" t="n">
         <v>1.18</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -28555,28 +28856,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04425221635744581</v>
+        <v>0.03736755278285007</v>
       </c>
       <c r="J2" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K2" t="n">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003330384335343273</v>
+        <v>0.002428949742588782</v>
       </c>
       <c r="M2" t="n">
-        <v>4.617018745218176</v>
+        <v>4.601192352023192</v>
       </c>
       <c r="N2" t="n">
-        <v>32.1845296014695</v>
+        <v>31.94759562566572</v>
       </c>
       <c r="O2" t="n">
-        <v>5.673141070118872</v>
+        <v>5.652220415523948</v>
       </c>
       <c r="P2" t="n">
-        <v>366.6409347423071</v>
+        <v>366.7139360223492</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28633,28 +28934,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.04944033791635823</v>
+        <v>-0.05311484888961451</v>
       </c>
       <c r="J3" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K3" t="n">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01294278072386046</v>
+        <v>0.01523368465907371</v>
       </c>
       <c r="M3" t="n">
-        <v>2.543487939836529</v>
+        <v>2.535507395415912</v>
       </c>
       <c r="N3" t="n">
-        <v>10.2375926481324</v>
+        <v>10.15976542991103</v>
       </c>
       <c r="O3" t="n">
-        <v>3.19962382916061</v>
+        <v>3.187438694298454</v>
       </c>
       <c r="P3" t="n">
-        <v>375.9841130349004</v>
+        <v>376.0230553097896</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -28711,28 +29012,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.007995529205914943</v>
+        <v>-0.01544560003096692</v>
       </c>
       <c r="J4" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K4" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0002662936471771182</v>
+        <v>0.00100817891720284</v>
       </c>
       <c r="M4" t="n">
-        <v>2.778593175617947</v>
+        <v>2.78700297224756</v>
       </c>
       <c r="N4" t="n">
-        <v>13.24886583117812</v>
+        <v>13.23666106078325</v>
       </c>
       <c r="O4" t="n">
-        <v>3.639899151237314</v>
+        <v>3.638222239058968</v>
       </c>
       <c r="P4" t="n">
-        <v>370.5690589771588</v>
+        <v>370.6477207675647</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -28789,28 +29090,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.05312927344662172</v>
+        <v>-0.0553614206883524</v>
       </c>
       <c r="J5" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K5" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01332714877216201</v>
+        <v>0.01479805277120294</v>
       </c>
       <c r="M5" t="n">
-        <v>2.511644060276128</v>
+        <v>2.494557090332985</v>
       </c>
       <c r="N5" t="n">
-        <v>11.53624396236514</v>
+        <v>11.42561802967852</v>
       </c>
       <c r="O5" t="n">
-        <v>3.396504668385595</v>
+        <v>3.38018017710277</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3548211561448</v>
+        <v>378.3783840057839</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28867,28 +29168,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.07706794697409271</v>
+        <v>-0.08042610012323238</v>
       </c>
       <c r="J6" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K6" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03468482475678947</v>
+        <v>0.03847107298576957</v>
       </c>
       <c r="M6" t="n">
-        <v>2.288185952190549</v>
+        <v>2.278179287133387</v>
       </c>
       <c r="N6" t="n">
-        <v>9.090339519078046</v>
+        <v>9.018098256968155</v>
       </c>
       <c r="O6" t="n">
-        <v>3.015018991495418</v>
+        <v>3.003014861263286</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2741824967295</v>
+        <v>379.3097714165591</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28945,28 +29246,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01866848959206302</v>
+        <v>-0.0212795667208052</v>
       </c>
       <c r="J7" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K7" t="n">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001533277958459256</v>
+        <v>0.002039107859373335</v>
       </c>
       <c r="M7" t="n">
-        <v>2.834203331798542</v>
+        <v>2.814401183897321</v>
       </c>
       <c r="N7" t="n">
-        <v>12.48055681517607</v>
+        <v>12.36208636482647</v>
       </c>
       <c r="O7" t="n">
-        <v>3.532783154281631</v>
+        <v>3.515975876599053</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6626066882617</v>
+        <v>378.6902771505561</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29023,28 +29324,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01190953702443593</v>
+        <v>0.006900817372580304</v>
       </c>
       <c r="J8" t="n">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="K8" t="n">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0006322092679450497</v>
+        <v>0.0002167353569673125</v>
       </c>
       <c r="M8" t="n">
-        <v>2.781582256650367</v>
+        <v>2.774427559655532</v>
       </c>
       <c r="N8" t="n">
-        <v>12.3727815840151</v>
+        <v>12.29492121861807</v>
       </c>
       <c r="O8" t="n">
-        <v>3.517496493817029</v>
+        <v>3.50641144457094</v>
       </c>
       <c r="P8" t="n">
-        <v>384.9966506758573</v>
+        <v>385.0497201728708</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29082,7 +29383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I644"/>
+  <dimension ref="A1:I651"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59305,6 +59606,335 @@
         </is>
       </c>
     </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>-36.55619681313588,174.7074679137925</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>-36.556890806539805,174.7073396186706</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>-36.55759764135715,174.7073205614735</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>-36.5582948811924,174.70754026954697</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>-36.558993575454664,174.70772142197472</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>-36.559690095893856,174.7079424493951</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>-36.56037743449841,174.70820601271421</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>-36.556195872407265,174.7074626799576</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>-36.556890897660814,174.70734117856256</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>-36.557597448790254,174.70732278295807</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>-36.55829449386501,174.70754302083438</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>-36.55899466585339,174.70771554269888</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>-36.559690443760125,174.70794071472145</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>-36.5603773058125,174.70820666376216</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>-36.55619579401321,174.70746224380466</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>-36.55689065684095,174.7073370559909</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>-36.557597477675294,174.7073224497354</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>-36.55829536147827,174.70753685795052</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>-36.55899589759975,174.70770890129447</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>-36.559692509215616,174.70793041509634</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>-36.5603790645195,174.7081977661066</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>-36.55619561762656,174.70746126246064</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>-36.556891711240354,174.70735510616956</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>-36.55759660149545,174.70733255748996</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>-36.558293967099644,174.70754676258528</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>-36.558995271630316,174.70771227643442</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>-36.5596917917417,174.70793399286092</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>-36.56037685541183,174.70820894242996</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>-36.55619416733606,174.70745319363212</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>-36.55689141835191,174.70735009223102</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>-36.55759625487462,174.70733655616203</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>-36.55829362625142,174.70754918371816</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>-36.55899517066751,174.70771282081185</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>-36.559691226459144,174.70793681170568</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>-36.560377091335994,174.70820774884206</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>-36.55619354018323,174.70744970440904</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>-36.556891125463245,174.7073450782925</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>-36.55759580234167,174.70734177665054</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>-36.558293781182435,174.7075480832032</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>-36.55899549374851,174.70771107880412</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>-36.5596917917417,174.70793399286092</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>-36.56037814227079,174.7082024319504</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>-36.55619205069487,174.70744141750447</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>-36.55689127516193,174.7073476409722</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>-36.55759539795034,174.7073464417678</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>-36.558292944554815,174.70755402598385</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>-36.55899498893444,174.70771380069118</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>-36.559690813368015,174.7079388716307</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>-36.560376941202435,174.708208508398</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0135/nzd0135.xlsx
+++ b/data/nzd0135/nzd0135.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I651"/>
+  <dimension ref="A1:I655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21899,6 +21899,138 @@
         <v>383.3</v>
       </c>
       <c r="I651" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="n">
+        <v>362.68</v>
+      </c>
+      <c r="C652" t="n">
+        <v>374.02</v>
+      </c>
+      <c r="D652" t="n">
+        <v>369.63</v>
+      </c>
+      <c r="E652" t="n">
+        <v>377.81</v>
+      </c>
+      <c r="F652" t="n">
+        <v>376.64</v>
+      </c>
+      <c r="G652" t="n">
+        <v>378.48</v>
+      </c>
+      <c r="H652" t="n">
+        <v>385.67</v>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="n">
+        <v>361.73</v>
+      </c>
+      <c r="C653" t="n">
+        <v>374.16</v>
+      </c>
+      <c r="D653" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="E653" t="n">
+        <v>378.38</v>
+      </c>
+      <c r="F653" t="n">
+        <v>377.82</v>
+      </c>
+      <c r="G653" t="n">
+        <v>379.29</v>
+      </c>
+      <c r="H653" t="n">
+        <v>386.44</v>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="n">
+        <v>361.89</v>
+      </c>
+      <c r="C654" t="n">
+        <v>374.1</v>
+      </c>
+      <c r="D654" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="E654" t="n">
+        <v>378.63</v>
+      </c>
+      <c r="F654" t="n">
+        <v>378.55</v>
+      </c>
+      <c r="G654" t="n">
+        <v>379.82</v>
+      </c>
+      <c r="H654" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="C655" t="n">
+        <v>373.05</v>
+      </c>
+      <c r="D655" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="E655" t="n">
+        <v>378.74</v>
+      </c>
+      <c r="F655" t="n">
+        <v>377.97</v>
+      </c>
+      <c r="G655" t="n">
+        <v>379.78</v>
+      </c>
+      <c r="H655" t="n">
+        <v>387.16</v>
+      </c>
+      <c r="I655" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -21915,7 +22047,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B677"/>
+  <dimension ref="A1:B681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28688,6 +28820,46 @@
       </c>
       <c r="B677" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>1.04</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -28856,28 +29028,28 @@
         <v>0.1028</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03736755278285007</v>
+        <v>0.03023677509219024</v>
       </c>
       <c r="J2" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K2" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002428949742588782</v>
+        <v>0.001604070390815782</v>
       </c>
       <c r="M2" t="n">
-        <v>4.601192352023192</v>
+        <v>4.607879718379364</v>
       </c>
       <c r="N2" t="n">
-        <v>31.94759562566572</v>
+        <v>31.95425785670143</v>
       </c>
       <c r="O2" t="n">
-        <v>5.652220415523948</v>
+        <v>5.652809731160374</v>
       </c>
       <c r="P2" t="n">
-        <v>366.7139360223492</v>
+        <v>366.7898509334265</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -28934,28 +29106,28 @@
         <v>0.06279999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.05311484888961451</v>
+        <v>-0.05405523878778751</v>
       </c>
       <c r="J3" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K3" t="n">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01523368465907371</v>
+        <v>0.01598221725599014</v>
       </c>
       <c r="M3" t="n">
-        <v>2.535507395415912</v>
+        <v>2.525001442740197</v>
       </c>
       <c r="N3" t="n">
-        <v>10.15976542991103</v>
+        <v>10.10229192559951</v>
       </c>
       <c r="O3" t="n">
-        <v>3.187438694298454</v>
+        <v>3.178410282767081</v>
       </c>
       <c r="P3" t="n">
-        <v>376.0230553097896</v>
+        <v>376.0330703617918</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -29012,28 +29184,28 @@
         <v>0.0936</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.01544560003096692</v>
+        <v>-0.0148677167972793</v>
       </c>
       <c r="J4" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K4" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00100817891720284</v>
+        <v>0.0009471411849558686</v>
       </c>
       <c r="M4" t="n">
-        <v>2.78700297224756</v>
+        <v>2.774539194808686</v>
       </c>
       <c r="N4" t="n">
-        <v>13.23666106078325</v>
+        <v>13.15985199248682</v>
       </c>
       <c r="O4" t="n">
-        <v>3.638222239058968</v>
+        <v>3.627651029590197</v>
       </c>
       <c r="P4" t="n">
-        <v>370.6477207675647</v>
+        <v>370.641585483087</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -29090,28 +29262,28 @@
         <v>0.0602</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0553614206883524</v>
+        <v>-0.05351668955113336</v>
       </c>
       <c r="J5" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K5" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01479805277120294</v>
+        <v>0.01401756807880028</v>
       </c>
       <c r="M5" t="n">
-        <v>2.494557090332985</v>
+        <v>2.489229505820269</v>
       </c>
       <c r="N5" t="n">
-        <v>11.42561802967852</v>
+        <v>11.37008428877115</v>
       </c>
       <c r="O5" t="n">
-        <v>3.38018017710277</v>
+        <v>3.371955558540348</v>
       </c>
       <c r="P5" t="n">
-        <v>378.3783840057839</v>
+        <v>378.3588141770585</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -29168,28 +29340,28 @@
         <v>0.0751</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.08042610012323238</v>
+        <v>-0.07968596358966039</v>
       </c>
       <c r="J6" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K6" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03847107298576957</v>
+        <v>0.03828769003908594</v>
       </c>
       <c r="M6" t="n">
-        <v>2.278179287133387</v>
+        <v>2.26980033411962</v>
       </c>
       <c r="N6" t="n">
-        <v>9.018098256968155</v>
+        <v>8.967882039040081</v>
       </c>
       <c r="O6" t="n">
-        <v>3.003014861263286</v>
+        <v>2.994642222209538</v>
       </c>
       <c r="P6" t="n">
-        <v>379.3097714165591</v>
+        <v>379.3018912221435</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -29246,28 +29418,28 @@
         <v>0.0667</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0212795667208052</v>
+        <v>-0.01976968509575223</v>
       </c>
       <c r="J7" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K7" t="n">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002039107859373335</v>
+        <v>0.001783869322059206</v>
       </c>
       <c r="M7" t="n">
-        <v>2.814401183897321</v>
+        <v>2.805712503211597</v>
       </c>
       <c r="N7" t="n">
-        <v>12.36208636482647</v>
+        <v>12.2970593796223</v>
       </c>
       <c r="O7" t="n">
-        <v>3.515975876599053</v>
+        <v>3.506716324372745</v>
       </c>
       <c r="P7" t="n">
-        <v>378.6902771505561</v>
+        <v>378.6742052455782</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -29324,28 +29496,28 @@
         <v>0.1107</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006900817372580304</v>
+        <v>0.008606343474684846</v>
       </c>
       <c r="J8" t="n">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="K8" t="n">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002167353569673125</v>
+        <v>0.0003414442142336549</v>
       </c>
       <c r="M8" t="n">
-        <v>2.774427559655532</v>
+        <v>2.766222328912244</v>
       </c>
       <c r="N8" t="n">
-        <v>12.29492121861807</v>
+        <v>12.23304322542828</v>
       </c>
       <c r="O8" t="n">
-        <v>3.50641144457094</v>
+        <v>3.497576764765611</v>
       </c>
       <c r="P8" t="n">
-        <v>385.0497201728708</v>
+        <v>385.0315653440128</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -29383,7 +29555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I651"/>
+  <dimension ref="A1:I655"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59935,6 +60107,194 @@
         </is>
       </c>
     </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>-36.55619093357821,174.70743520232622</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>-36.5568918088698,174.70735677748243</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>-36.55759404997787,174.70736199215844</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>-36.55829119383308,174.70756646180214</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>-36.558993050447775,174.7077242527371</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>-36.55968794347072,174.70795318268793</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>-36.5603718581062,174.7082342247901</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>-36.55618907171638,174.7074248436962</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>-36.55689189999058,174.70735833737442</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>-36.55759306788239,174.70737332172834</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>-36.55829031072518,174.70757273473683</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>-36.55899066772337,174.70773710004278</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>-36.55968618239655,174.70796196447247</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>-36.56037020663492,174.70824257990404</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>-36.556189385293166,174.70742658830756</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>-36.556891860938826,174.70735766884928</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>-36.557592634604624,174.70737832006787</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>-36.55828992339704,174.70757548602393</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>-36.55898919366436,174.70774504795182</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>-36.5596850300884,174.7079677105782</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>-36.560368555163066,174.70825093501762</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:30+00:00</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>-36.556188483759826,174.70742157255</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>-36.556891177532364,174.70734596965934</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>-36.55759231686748,174.70738198551686</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>-36.55828975297265,174.70757669659022</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>-36.558990364834564,174.7077387331748</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>-36.559685117055075,174.70796727690984</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>-36.56036866240153,174.70825039247777</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
